--- a/wwwroot/template/Template_Import_Material.xlsx
+++ b/wwwroot/template/Template_Import_Material.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\17_KhoWeb\wwwroot\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{594B0F05-6646-4EF4-B6A7-B31C308C02E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5185386B-F236-4E15-9098-60E6C30E5888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42438605-012C-4D21-8453-1B584DCD9141}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{42438605-012C-4D21-8453-1B584DCD9141}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -706,18 +706,10 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1">
-        <v>1233333</v>
-      </c>
-      <c r="G5" s="1">
-        <v>123</v>
-      </c>
-      <c r="H5" s="1">
-        <v>123</v>
-      </c>
-      <c r="I5" s="1">
-        <v>12</v>
-      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1084,11 +1076,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="H3:H4"/>
@@ -1102,6 +1089,11 @@
     <mergeCell ref="L3:P3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
